--- a/automotive_forms/018_rv_battery_recommendation_request_form--automotive_forms.xlsx
+++ b/automotive_forms/018_rv_battery_recommendation_request_form--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>follow_up_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Follow Up</t>
+          <t>Follow Up 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>assigned_to_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Assigned To</t>
+          <t>Assigned To 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>comments_to</t>
+          <t>comments_to_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments To</t>
+          <t>Comments To 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>service_center</t>
+          <t>service_center_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Service Center</t>
+          <t>Service Center 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Location 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>assigned_to_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Assigned To</t>
+          <t>Assigned To 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1199,46 +1199,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>class_c_motorhome</t>
+          <t>truck_camper</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Class C Motorhome</t>
+          <t>Truck Camper</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>camping_style_choices</t>
+          <t>camping_goals_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>class_a_motorhome</t>
+          <t>camping_in_the_mountains</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Class A Motorhome</t>
+          <t>Camping in the mountains</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>camping_style_choices</t>
+          <t>camping_goals_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>truck_camper</t>
+          <t>dry_camping</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Truck Camper</t>
+          <t>Dry Camping</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>camping_in_the_mountains</t>
+          <t>boondocking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Camping in the mountains</t>
+          <t>Boondocking</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dry_camping</t>
+          <t>remote_camping</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dry Camping</t>
+          <t>Remote Camping</t>
         </is>
       </c>
     </row>
@@ -1284,46 +1284,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>boondocking</t>
+          <t>full_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boondocking</t>
+          <t>Full Service</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>camping_goals_choices</t>
+          <t>power_goals_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>remote_camping</t>
+          <t>less_than_20_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote Camping</t>
+          <t>Less than 20 hours</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>camping_goals_choices</t>
+          <t>power_goals_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>full_service</t>
+          <t>20-40_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Full Service</t>
+          <t>20-40 hours</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>less_than_20_hours</t>
+          <t>40-60_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Less than 20 hours</t>
+          <t>40-60 hours</t>
         </is>
       </c>
     </row>
@@ -1352,46 +1352,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20-40_hours</t>
+          <t>more_than_60_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20-40 hours</t>
+          <t>More than 60 hours</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>power_goals_choices</t>
+          <t>battery_amps_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>40-60_hours</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>40-60 hours</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>power_goals_choices</t>
+          <t>battery_amps_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>more_than_60_hours</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>More than 60 hours</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1403,384 +1403,248 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>battery_amps_choices</t>
+          <t>battery_volt_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>battery_amps_choices</t>
+          <t>battery_volt_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>battery_amps_choices</t>
+          <t>battery_volt_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>battery_amps_choices</t>
+          <t>deep_cycle_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>battery_amps_choices</t>
+          <t>deep_cycle_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>battery_amps_choices</t>
+          <t>battery_brand_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>trojan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Trojan</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>battery_amps_choices</t>
+          <t>battery_brand_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>century</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Century</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>battery_volt_choices</t>
+          <t>battery_brand_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>deka</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Deka</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>battery_volt_choices</t>
+          <t>battery_brand_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>exide</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Exide</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>battery_volt_choices</t>
+          <t>battery_brand_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>north_star</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>North Star</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>battery_volt_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>deep_cycle_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>deep_cycle_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>battery_brand_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>trojan</t>
+          <t>no_follow_up</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>battery_brand_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>century</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Century</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>battery_brand_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>deka</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Deka</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>battery_brand_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>exide</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Exide</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>battery_brand_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>north_star</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>North Star</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>mail</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mail</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>no_follow_up</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>No Follow Up</t>
         </is>
